--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,14 +874,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,14 +975,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,14 +1081,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1187,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>126318095</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126318102</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126318101</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126318103</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>126318105</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126318102</v>
+        <v>126318098</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762573</v>
+        <v>762613</v>
       </c>
       <c r="R2" t="n">
-        <v>7180849</v>
+        <v>7180897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126318101</v>
+        <v>126318093</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762545</v>
+        <v>762613</v>
       </c>
       <c r="R3" t="n">
-        <v>7180758</v>
+        <v>7180897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126318095</v>
+        <v>126318101</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762579</v>
+        <v>762545</v>
       </c>
       <c r="R4" t="n">
-        <v>7180818</v>
+        <v>7180758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,14 +983,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126318103</v>
+        <v>126318102</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762671</v>
+        <v>762573</v>
       </c>
       <c r="R5" t="n">
-        <v>7180903</v>
+        <v>7180849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,11 +1054,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,14 +1084,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126318105</v>
+        <v>126318103</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762729</v>
+        <v>762671</v>
       </c>
       <c r="R6" t="n">
-        <v>7180918</v>
+        <v>7180903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1159,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långa bålar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,6 +1183,213 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126318105</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällbergsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>762729</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7180918</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126318095</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällbergsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>762579</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7180818</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 26962-2025 artfynd.xlsx
+++ b/artfynd/A 26962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318093</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318102</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318105</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,8 +1429,22 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126318095</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>